--- a/data/provinces/shaanxi.xlsx
+++ b/data/provinces/shaanxi.xlsx
@@ -134,7 +134,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>2.2011—2019</t>
+      <t>2.2011~2019</t>
     </r>
     <r>
       <rPr>
